--- a/assets/class4/avocados.xlsx
+++ b/assets/class4/avocados.xlsx
@@ -11,6 +11,20 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>conventional</t>
+  </si>
+  <si>
+    <t>organic</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57,10 +71,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -358,28 +372,22 @@
   <dimension ref="A1:C170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>conventional</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>organic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
+    <row r="1" spans="1:3" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
         <v>42008</v>
       </c>
       <c r="B2">
@@ -389,8 +397,8 @@
         <v>1.592962962962963</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>42015</v>
       </c>
       <c r="B3">
@@ -400,8 +408,8 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
         <v>42022</v>
       </c>
       <c r="B4">
@@ -411,8 +419,8 @@
         <v>1.648703703703704</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
         <v>42029</v>
       </c>
       <c r="B5">
@@ -422,8 +430,8 @@
         <v>1.678888888888889</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
         <v>42036</v>
       </c>
       <c r="B6">
@@ -433,8 +441,8 @@
         <v>1.532037037037037</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
         <v>42043</v>
       </c>
       <c r="B7">
@@ -444,8 +452,8 @@
         <v>1.590555555555556</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
         <v>42050</v>
       </c>
       <c r="B8">
@@ -455,8 +463,8 @@
         <v>1.646111111111111</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2">
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
         <v>42057</v>
       </c>
       <c r="B9">
@@ -466,8 +474,8 @@
         <v>1.625555555555556</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2">
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
         <v>42064</v>
       </c>
       <c r="B10">
@@ -477,8 +485,8 @@
         <v>1.585185185185185</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2">
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
         <v>42071</v>
       </c>
       <c r="B11">
@@ -488,8 +496,8 @@
         <v>1.611296296296296</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
         <v>42078</v>
       </c>
       <c r="B12">
@@ -499,8 +507,8 @@
         <v>1.642962962962963</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
         <v>42085</v>
       </c>
       <c r="B13">
@@ -510,8 +518,8 @@
         <v>1.639074074074074</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2">
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
         <v>42092</v>
       </c>
       <c r="B14">
@@ -521,8 +529,8 @@
         <v>1.691851851851852</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2">
+    <row r="15" spans="1:3">
+      <c r="A15" s="1">
         <v>42099</v>
       </c>
       <c r="B15">
@@ -532,8 +540,8 @@
         <v>1.692592592592593</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2">
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
         <v>42106</v>
       </c>
       <c r="B16">
@@ -543,8 +551,8 @@
         <v>1.633148148148148</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2">
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
         <v>42113</v>
       </c>
       <c r="B17">
@@ -554,8 +562,8 @@
         <v>1.643703703703704</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2">
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
         <v>42120</v>
       </c>
       <c r="B18">
@@ -565,8 +573,8 @@
         <v>1.630740740740741</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2">
+    <row r="19" spans="1:3">
+      <c r="A19" s="1">
         <v>42127</v>
       </c>
       <c r="B19">
@@ -576,8 +584,8 @@
         <v>1.549814814814815</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1">
         <v>42134</v>
       </c>
       <c r="B20">
@@ -587,8 +595,8 @@
         <v>1.547777777777778</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2">
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
         <v>42141</v>
       </c>
       <c r="B21">
@@ -598,8 +606,8 @@
         <v>1.581111111111111</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2">
+    <row r="22" spans="1:3">
+      <c r="A22" s="1">
         <v>42148</v>
       </c>
       <c r="B22">
@@ -609,8 +617,8 @@
         <v>1.670185185185185</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2">
+    <row r="23" spans="1:3">
+      <c r="A23" s="1">
         <v>42155</v>
       </c>
       <c r="B23">
@@ -620,8 +628,8 @@
         <v>1.64537037037037</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2">
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
         <v>42162</v>
       </c>
       <c r="B24">
@@ -631,8 +639,8 @@
         <v>1.685740740740741</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2">
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
         <v>42169</v>
       </c>
       <c r="B25">
@@ -642,8 +650,8 @@
         <v>1.723703703703704</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2">
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
         <v>42176</v>
       </c>
       <c r="B26">
@@ -653,8 +661,8 @@
         <v>1.73962962962963</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2">
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
         <v>42183</v>
       </c>
       <c r="B27">
@@ -664,8 +672,8 @@
         <v>1.697592592592593</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2">
+    <row r="28" spans="1:3">
+      <c r="A28" s="1">
         <v>42190</v>
       </c>
       <c r="B28">
@@ -675,8 +683,8 @@
         <v>1.722777777777778</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2">
+    <row r="29" spans="1:3">
+      <c r="A29" s="1">
         <v>42197</v>
       </c>
       <c r="B29">
@@ -686,8 +694,8 @@
         <v>1.719259259259259</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2">
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
         <v>42204</v>
       </c>
       <c r="B30">
@@ -697,8 +705,8 @@
         <v>1.665555555555555</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2">
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
         <v>42211</v>
       </c>
       <c r="B31">
@@ -708,8 +716,8 @@
         <v>1.712407407407407</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2">
+    <row r="32" spans="1:3">
+      <c r="A32" s="1">
         <v>42218</v>
       </c>
       <c r="B32">
@@ -719,8 +727,8 @@
         <v>1.811111111111111</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2">
+    <row r="33" spans="1:3">
+      <c r="A33" s="1">
         <v>42225</v>
       </c>
       <c r="B33">
@@ -730,8 +738,8 @@
         <v>1.779814814814815</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2">
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
         <v>42232</v>
       </c>
       <c r="B34">
@@ -741,8 +749,8 @@
         <v>1.79037037037037</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2">
+    <row r="35" spans="1:3">
+      <c r="A35" s="1">
         <v>42239</v>
       </c>
       <c r="B35">
@@ -752,8 +760,8 @@
         <v>1.763333333333333</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2">
+    <row r="36" spans="1:3">
+      <c r="A36" s="1">
         <v>42246</v>
       </c>
       <c r="B36">
@@ -763,8 +771,8 @@
         <v>1.715</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
         <v>42253</v>
       </c>
       <c r="B37">
@@ -774,8 +782,8 @@
         <v>1.798888888888889</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2">
+    <row r="38" spans="1:3">
+      <c r="A38" s="1">
         <v>42260</v>
       </c>
       <c r="B38">
@@ -785,8 +793,8 @@
         <v>1.843703703703704</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2">
+    <row r="39" spans="1:3">
+      <c r="A39" s="1">
         <v>42267</v>
       </c>
       <c r="B39">
@@ -796,8 +804,8 @@
         <v>1.827592592592593</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2">
+    <row r="40" spans="1:3">
+      <c r="A40" s="1">
         <v>42274</v>
       </c>
       <c r="B40">
@@ -807,8 +815,8 @@
         <v>1.821851851851852</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2">
+    <row r="41" spans="1:3">
+      <c r="A41" s="1">
         <v>42281</v>
       </c>
       <c r="B41">
@@ -818,8 +826,8 @@
         <v>1.770740740740741</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2">
+    <row r="42" spans="1:3">
+      <c r="A42" s="1">
         <v>42288</v>
       </c>
       <c r="B42">
@@ -829,8 +837,8 @@
         <v>1.702222222222222</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2">
+    <row r="43" spans="1:3">
+      <c r="A43" s="1">
         <v>42295</v>
       </c>
       <c r="B43">
@@ -840,8 +848,8 @@
         <v>1.734259259259259</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2">
+    <row r="44" spans="1:3">
+      <c r="A44" s="1">
         <v>42302</v>
       </c>
       <c r="B44">
@@ -851,8 +859,8 @@
         <v>1.672592592592593</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2">
+    <row r="45" spans="1:3">
+      <c r="A45" s="1">
         <v>42309</v>
       </c>
       <c r="B45">
@@ -862,8 +870,8 @@
         <v>1.601851851851852</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2">
+    <row r="46" spans="1:3">
+      <c r="A46" s="1">
         <v>42316</v>
       </c>
       <c r="B46">
@@ -873,8 +881,8 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2">
+    <row r="47" spans="1:3">
+      <c r="A47" s="1">
         <v>42323</v>
       </c>
       <c r="B47">
@@ -884,8 +892,8 @@
         <v>1.667222222222222</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2">
+    <row r="48" spans="1:3">
+      <c r="A48" s="1">
         <v>42330</v>
       </c>
       <c r="B48">
@@ -895,8 +903,8 @@
         <v>1.632222222222222</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2">
+    <row r="49" spans="1:3">
+      <c r="A49" s="1">
         <v>42337</v>
       </c>
       <c r="B49">
@@ -906,8 +914,8 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2">
+    <row r="50" spans="1:3">
+      <c r="A50" s="1">
         <v>42344</v>
       </c>
       <c r="B50">
@@ -917,8 +925,8 @@
         <v>1.610943396226415</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2">
+    <row r="51" spans="1:3">
+      <c r="A51" s="1">
         <v>42351</v>
       </c>
       <c r="B51">
@@ -928,8 +936,8 @@
         <v>1.59037037037037</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2">
+    <row r="52" spans="1:3">
+      <c r="A52" s="1">
         <v>42358</v>
       </c>
       <c r="B52">
@@ -939,8 +947,8 @@
         <v>1.638518518518518</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2">
+    <row r="53" spans="1:3">
+      <c r="A53" s="1">
         <v>42365</v>
       </c>
       <c r="B53">
@@ -950,8 +958,8 @@
         <v>1.582777777777778</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2">
+    <row r="54" spans="1:3">
+      <c r="A54" s="1">
         <v>42372</v>
       </c>
       <c r="B54">
@@ -961,8 +969,8 @@
         <v>1.47037037037037</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2">
+    <row r="55" spans="1:3">
+      <c r="A55" s="1">
         <v>42379</v>
       </c>
       <c r="B55">
@@ -972,8 +980,8 @@
         <v>1.460925925925926</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2">
+    <row r="56" spans="1:3">
+      <c r="A56" s="1">
         <v>42386</v>
       </c>
       <c r="B56">
@@ -983,8 +991,8 @@
         <v>1.527962962962963</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2">
+    <row r="57" spans="1:3">
+      <c r="A57" s="1">
         <v>42393</v>
       </c>
       <c r="B57">
@@ -994,8 +1002,8 @@
         <v>1.492222222222222</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2">
+    <row r="58" spans="1:3">
+      <c r="A58" s="1">
         <v>42400</v>
       </c>
       <c r="B58">
@@ -1005,8 +1013,8 @@
         <v>1.520740740740741</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2">
+    <row r="59" spans="1:3">
+      <c r="A59" s="1">
         <v>42407</v>
       </c>
       <c r="B59">
@@ -1016,8 +1024,8 @@
         <v>1.525555555555556</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2">
+    <row r="60" spans="1:3">
+      <c r="A60" s="1">
         <v>42414</v>
       </c>
       <c r="B60">
@@ -1027,8 +1035,8 @@
         <v>1.516296296296296</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2">
+    <row r="61" spans="1:3">
+      <c r="A61" s="1">
         <v>42421</v>
       </c>
       <c r="B61">
@@ -1038,8 +1046,8 @@
         <v>1.546111111111111</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2">
+    <row r="62" spans="1:3">
+      <c r="A62" s="1">
         <v>42428</v>
       </c>
       <c r="B62">
@@ -1049,8 +1057,8 @@
         <v>1.55962962962963</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2">
+    <row r="63" spans="1:3">
+      <c r="A63" s="1">
         <v>42435</v>
       </c>
       <c r="B63">
@@ -1060,8 +1068,8 @@
         <v>1.497222222222222</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2">
+    <row r="64" spans="1:3">
+      <c r="A64" s="1">
         <v>42442</v>
       </c>
       <c r="B64">
@@ -1071,8 +1079,8 @@
         <v>1.419259259259259</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2">
+    <row r="65" spans="1:3">
+      <c r="A65" s="1">
         <v>42449</v>
       </c>
       <c r="B65">
@@ -1082,8 +1090,8 @@
         <v>1.391296296296296</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2">
+    <row r="66" spans="1:3">
+      <c r="A66" s="1">
         <v>42456</v>
       </c>
       <c r="B66">
@@ -1093,8 +1101,8 @@
         <v>1.480740740740741</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2">
+    <row r="67" spans="1:3">
+      <c r="A67" s="1">
         <v>42463</v>
       </c>
       <c r="B67">
@@ -1104,8 +1112,8 @@
         <v>1.483888888888889</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2">
+    <row r="68" spans="1:3">
+      <c r="A68" s="1">
         <v>42470</v>
       </c>
       <c r="B68">
@@ -1115,8 +1123,8 @@
         <v>1.382592592592593</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2">
+    <row r="69" spans="1:3">
+      <c r="A69" s="1">
         <v>42477</v>
       </c>
       <c r="B69">
@@ -1126,8 +1134,8 @@
         <v>1.477222222222222</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2">
+    <row r="70" spans="1:3">
+      <c r="A70" s="1">
         <v>42484</v>
       </c>
       <c r="B70">
@@ -1137,8 +1145,8 @@
         <v>1.452037037037037</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2">
+    <row r="71" spans="1:3">
+      <c r="A71" s="1">
         <v>42491</v>
       </c>
       <c r="B71">
@@ -1148,8 +1156,8 @@
         <v>1.437962962962963</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2">
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
         <v>42498</v>
       </c>
       <c r="B72">
@@ -1159,8 +1167,8 @@
         <v>1.423888888888889</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2">
+    <row r="73" spans="1:3">
+      <c r="A73" s="1">
         <v>42505</v>
       </c>
       <c r="B73">
@@ -1170,8 +1178,8 @@
         <v>1.504259259259259</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2">
+    <row r="74" spans="1:3">
+      <c r="A74" s="1">
         <v>42512</v>
       </c>
       <c r="B74">
@@ -1181,8 +1189,8 @@
         <v>1.452962962962963</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2">
+    <row r="75" spans="1:3">
+      <c r="A75" s="1">
         <v>42519</v>
       </c>
       <c r="B75">
@@ -1192,8 +1200,8 @@
         <v>1.497037037037037</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2">
+    <row r="76" spans="1:3">
+      <c r="A76" s="1">
         <v>42526</v>
       </c>
       <c r="B76">
@@ -1203,8 +1211,8 @@
         <v>1.462407407407407</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2">
+    <row r="77" spans="1:3">
+      <c r="A77" s="1">
         <v>42533</v>
       </c>
       <c r="B77">
@@ -1214,8 +1222,8 @@
         <v>1.504814814814815</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2">
+    <row r="78" spans="1:3">
+      <c r="A78" s="1">
         <v>42540</v>
       </c>
       <c r="B78">
@@ -1225,8 +1233,8 @@
         <v>1.482222222222222</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2">
+    <row r="79" spans="1:3">
+      <c r="A79" s="1">
         <v>42547</v>
       </c>
       <c r="B79">
@@ -1236,8 +1244,8 @@
         <v>1.524814814814815</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2">
+    <row r="80" spans="1:3">
+      <c r="A80" s="1">
         <v>42554</v>
       </c>
       <c r="B80">
@@ -1247,8 +1255,8 @@
         <v>1.495740740740741</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2">
+    <row r="81" spans="1:3">
+      <c r="A81" s="1">
         <v>42561</v>
       </c>
       <c r="B81">
@@ -1258,8 +1266,8 @@
         <v>1.573148148148148</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2">
+    <row r="82" spans="1:3">
+      <c r="A82" s="1">
         <v>42568</v>
       </c>
       <c r="B82">
@@ -1269,8 +1277,8 @@
         <v>1.669259259259259</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2">
+    <row r="83" spans="1:3">
+      <c r="A83" s="1">
         <v>42575</v>
       </c>
       <c r="B83">
@@ -1280,8 +1288,8 @@
         <v>1.723333333333333</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2">
+    <row r="84" spans="1:3">
+      <c r="A84" s="1">
         <v>42582</v>
       </c>
       <c r="B84">
@@ -1291,8 +1299,8 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2">
+    <row r="85" spans="1:3">
+      <c r="A85" s="1">
         <v>42589</v>
       </c>
       <c r="B85">
@@ -1302,8 +1310,8 @@
         <v>1.617222222222222</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2">
+    <row r="86" spans="1:3">
+      <c r="A86" s="1">
         <v>42596</v>
       </c>
       <c r="B86">
@@ -1313,8 +1321,8 @@
         <v>1.67037037037037</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2">
+    <row r="87" spans="1:3">
+      <c r="A87" s="1">
         <v>42603</v>
       </c>
       <c r="B87">
@@ -1324,8 +1332,8 @@
         <v>1.658518518518519</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2">
+    <row r="88" spans="1:3">
+      <c r="A88" s="1">
         <v>42610</v>
       </c>
       <c r="B88">
@@ -1335,8 +1343,8 @@
         <v>1.623703703703704</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2">
+    <row r="89" spans="1:3">
+      <c r="A89" s="1">
         <v>42617</v>
       </c>
       <c r="B89">
@@ -1346,8 +1354,8 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2">
+    <row r="90" spans="1:3">
+      <c r="A90" s="1">
         <v>42624</v>
       </c>
       <c r="B90">
@@ -1357,8 +1365,8 @@
         <v>1.577777777777778</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2">
+    <row r="91" spans="1:3">
+      <c r="A91" s="1">
         <v>42631</v>
       </c>
       <c r="B91">
@@ -1368,8 +1376,8 @@
         <v>1.691666666666667</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2">
+    <row r="92" spans="1:3">
+      <c r="A92" s="1">
         <v>42638</v>
       </c>
       <c r="B92">
@@ -1379,8 +1387,8 @@
         <v>1.791666666666667</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2">
+    <row r="93" spans="1:3">
+      <c r="A93" s="1">
         <v>42645</v>
       </c>
       <c r="B93">
@@ -1390,8 +1398,8 @@
         <v>1.855185185185185</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2">
+    <row r="94" spans="1:3">
+      <c r="A94" s="1">
         <v>42652</v>
       </c>
       <c r="B94">
@@ -1401,8 +1409,8 @@
         <v>1.650740740740741</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2">
+    <row r="95" spans="1:3">
+      <c r="A95" s="1">
         <v>42659</v>
       </c>
       <c r="B95">
@@ -1412,8 +1420,8 @@
         <v>1.638703703703704</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2">
+    <row r="96" spans="1:3">
+      <c r="A96" s="1">
         <v>42666</v>
       </c>
       <c r="B96">
@@ -1423,8 +1431,8 @@
         <v>1.703703703703704</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2">
+    <row r="97" spans="1:3">
+      <c r="A97" s="1">
         <v>42673</v>
       </c>
       <c r="B97">
@@ -1434,8 +1442,8 @@
         <v>1.956111111111111</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2">
+    <row r="98" spans="1:3">
+      <c r="A98" s="1">
         <v>42680</v>
       </c>
       <c r="B98">
@@ -1445,8 +1453,8 @@
         <v>1.762777777777778</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2">
+    <row r="99" spans="1:3">
+      <c r="A99" s="1">
         <v>42687</v>
       </c>
       <c r="B99">
@@ -1456,8 +1464,8 @@
         <v>1.76462962962963</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2">
+    <row r="100" spans="1:3">
+      <c r="A100" s="1">
         <v>42694</v>
       </c>
       <c r="B100">
@@ -1467,8 +1475,8 @@
         <v>1.660185185185185</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2">
+    <row r="101" spans="1:3">
+      <c r="A101" s="1">
         <v>42701</v>
       </c>
       <c r="B101">
@@ -1478,8 +1486,8 @@
         <v>1.699814814814815</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2">
+    <row r="102" spans="1:3">
+      <c r="A102" s="1">
         <v>42708</v>
       </c>
       <c r="B102">
@@ -1489,8 +1497,8 @@
         <v>1.636111111111111</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2">
+    <row r="103" spans="1:3">
+      <c r="A103" s="1">
         <v>42715</v>
       </c>
       <c r="B103">
@@ -1500,8 +1508,8 @@
         <v>1.537962962962963</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2">
+    <row r="104" spans="1:3">
+      <c r="A104" s="1">
         <v>42722</v>
       </c>
       <c r="B104">
@@ -1511,8 +1519,8 @@
         <v>1.506851851851852</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2">
+    <row r="105" spans="1:3">
+      <c r="A105" s="1">
         <v>42729</v>
       </c>
       <c r="B105">
@@ -1522,8 +1530,8 @@
         <v>1.532962962962963</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2">
+    <row r="106" spans="1:3">
+      <c r="A106" s="1">
         <v>42736</v>
       </c>
       <c r="B106">
@@ -1533,8 +1541,8 @@
         <v>1.567407407407407</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2">
+    <row r="107" spans="1:3">
+      <c r="A107" s="1">
         <v>42743</v>
       </c>
       <c r="B107">
@@ -1544,8 +1552,8 @@
         <v>1.528888888888889</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2">
+    <row r="108" spans="1:3">
+      <c r="A108" s="1">
         <v>42750</v>
       </c>
       <c r="B108">
@@ -1555,8 +1563,8 @@
         <v>1.549444444444444</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2">
+    <row r="109" spans="1:3">
+      <c r="A109" s="1">
         <v>42757</v>
       </c>
       <c r="B109">
@@ -1566,8 +1574,8 @@
         <v>1.425555555555555</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2">
+    <row r="110" spans="1:3">
+      <c r="A110" s="1">
         <v>42764</v>
       </c>
       <c r="B110">
@@ -1577,8 +1585,8 @@
         <v>1.485925925925926</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2">
+    <row r="111" spans="1:3">
+      <c r="A111" s="1">
         <v>42771</v>
       </c>
       <c r="B111">
@@ -1588,8 +1596,8 @@
         <v>1.425740740740741</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2">
+    <row r="112" spans="1:3">
+      <c r="A112" s="1">
         <v>42778</v>
       </c>
       <c r="B112">
@@ -1599,8 +1607,8 @@
         <v>1.453333333333333</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2">
+    <row r="113" spans="1:3">
+      <c r="A113" s="1">
         <v>42785</v>
       </c>
       <c r="B113">
@@ -1610,8 +1618,8 @@
         <v>1.429259259259259</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2">
+    <row r="114" spans="1:3">
+      <c r="A114" s="1">
         <v>42792</v>
       </c>
       <c r="B114">
@@ -1621,8 +1629,8 @@
         <v>1.389074074074074</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2">
+    <row r="115" spans="1:3">
+      <c r="A115" s="1">
         <v>42799</v>
       </c>
       <c r="B115">
@@ -1632,8 +1640,8 @@
         <v>1.376851851851852</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2">
+    <row r="116" spans="1:3">
+      <c r="A116" s="1">
         <v>42806</v>
       </c>
       <c r="B116">
@@ -1643,8 +1651,8 @@
         <v>1.558703703703704</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2">
+    <row r="117" spans="1:3">
+      <c r="A117" s="1">
         <v>42813</v>
       </c>
       <c r="B117">
@@ -1654,8 +1662,8 @@
         <v>1.607407407407407</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2">
+    <row r="118" spans="1:3">
+      <c r="A118" s="1">
         <v>42820</v>
       </c>
       <c r="B118">
@@ -1665,8 +1673,8 @@
         <v>1.480185185185185</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2">
+    <row r="119" spans="1:3">
+      <c r="A119" s="1">
         <v>42827</v>
       </c>
       <c r="B119">
@@ -1676,8 +1684,8 @@
         <v>1.56537037037037</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2">
+    <row r="120" spans="1:3">
+      <c r="A120" s="1">
         <v>42834</v>
       </c>
       <c r="B120">
@@ -1687,8 +1695,8 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2">
+    <row r="121" spans="1:3">
+      <c r="A121" s="1">
         <v>42841</v>
       </c>
       <c r="B121">
@@ -1698,8 +1706,8 @@
         <v>1.681666666666667</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2">
+    <row r="122" spans="1:3">
+      <c r="A122" s="1">
         <v>42848</v>
       </c>
       <c r="B122">
@@ -1709,8 +1717,8 @@
         <v>1.788333333333333</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2">
+    <row r="123" spans="1:3">
+      <c r="A123" s="1">
         <v>42855</v>
       </c>
       <c r="B123">
@@ -1720,8 +1728,8 @@
         <v>1.827037037037037</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2">
+    <row r="124" spans="1:3">
+      <c r="A124" s="1">
         <v>42862</v>
       </c>
       <c r="B124">
@@ -1731,8 +1739,8 @@
         <v>1.760925925925926</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2">
+    <row r="125" spans="1:3">
+      <c r="A125" s="1">
         <v>42869</v>
       </c>
       <c r="B125">
@@ -1742,8 +1750,8 @@
         <v>1.771666666666667</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2">
+    <row r="126" spans="1:3">
+      <c r="A126" s="1">
         <v>42876</v>
       </c>
       <c r="B126">
@@ -1753,8 +1761,8 @@
         <v>1.797777777777778</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2">
+    <row r="127" spans="1:3">
+      <c r="A127" s="1">
         <v>42883</v>
       </c>
       <c r="B127">
@@ -1764,8 +1772,8 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2">
+    <row r="128" spans="1:3">
+      <c r="A128" s="1">
         <v>42890</v>
       </c>
       <c r="B128">
@@ -1775,8 +1783,8 @@
         <v>1.790555555555555</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2">
+    <row r="129" spans="1:3">
+      <c r="A129" s="1">
         <v>42897</v>
       </c>
       <c r="B129">
@@ -1786,8 +1794,8 @@
         <v>1.738148148148148</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2">
+    <row r="130" spans="1:3">
+      <c r="A130" s="1">
         <v>42904</v>
       </c>
       <c r="B130">
@@ -1797,8 +1805,8 @@
         <v>1.807924528301887</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2">
+    <row r="131" spans="1:3">
+      <c r="A131" s="1">
         <v>42911</v>
       </c>
       <c r="B131">
@@ -1808,8 +1816,8 @@
         <v>1.883396226415094</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2">
+    <row r="132" spans="1:3">
+      <c r="A132" s="1">
         <v>42918</v>
       </c>
       <c r="B132">
@@ -1819,8 +1827,8 @@
         <v>1.873703703703704</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2">
+    <row r="133" spans="1:3">
+      <c r="A133" s="1">
         <v>42925</v>
       </c>
       <c r="B133">
@@ -1830,8 +1838,8 @@
         <v>1.845925925925926</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2">
+    <row r="134" spans="1:3">
+      <c r="A134" s="1">
         <v>42932</v>
       </c>
       <c r="B134">
@@ -1841,8 +1849,8 @@
         <v>1.797962962962963</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2">
+    <row r="135" spans="1:3">
+      <c r="A135" s="1">
         <v>42939</v>
       </c>
       <c r="B135">
@@ -1852,8 +1860,8 @@
         <v>1.76962962962963</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2">
+    <row r="136" spans="1:3">
+      <c r="A136" s="1">
         <v>42946</v>
       </c>
       <c r="B136">
@@ -1863,8 +1871,8 @@
         <v>1.76962962962963</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2">
+    <row r="137" spans="1:3">
+      <c r="A137" s="1">
         <v>42953</v>
       </c>
       <c r="B137">
@@ -1874,8 +1882,8 @@
         <v>1.834074074074074</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2">
+    <row r="138" spans="1:3">
+      <c r="A138" s="1">
         <v>42960</v>
       </c>
       <c r="B138">
@@ -1885,8 +1893,8 @@
         <v>1.880555555555556</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2">
+    <row r="139" spans="1:3">
+      <c r="A139" s="1">
         <v>42967</v>
       </c>
       <c r="B139">
@@ -1896,8 +1904,8 @@
         <v>2.004074074074074</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2">
+    <row r="140" spans="1:3">
+      <c r="A140" s="1">
         <v>42974</v>
       </c>
       <c r="B140">
@@ -1907,8 +1915,8 @@
         <v>2.117037037037037</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2">
+    <row r="141" spans="1:3">
+      <c r="A141" s="1">
         <v>42981</v>
       </c>
       <c r="B141">
@@ -1918,8 +1926,8 @@
         <v>2.093703703703704</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2">
+    <row r="142" spans="1:3">
+      <c r="A142" s="1">
         <v>42988</v>
       </c>
       <c r="B142">
@@ -1929,8 +1937,8 @@
         <v>2.076481481481482</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2">
+    <row r="143" spans="1:3">
+      <c r="A143" s="1">
         <v>42995</v>
       </c>
       <c r="B143">
@@ -1940,8 +1948,8 @@
         <v>2.058703703703704</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2">
+    <row r="144" spans="1:3">
+      <c r="A144" s="1">
         <v>43002</v>
       </c>
       <c r="B144">
@@ -1951,8 +1959,8 @@
         <v>2.014814814814815</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2">
+    <row r="145" spans="1:3">
+      <c r="A145" s="1">
         <v>43009</v>
       </c>
       <c r="B145">
@@ -1962,8 +1970,8 @@
         <v>2.047962962962963</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2">
+    <row r="146" spans="1:3">
+      <c r="A146" s="1">
         <v>43016</v>
       </c>
       <c r="B146">
@@ -1973,8 +1981,8 @@
         <v>1.980740740740741</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2">
+    <row r="147" spans="1:3">
+      <c r="A147" s="1">
         <v>43023</v>
       </c>
       <c r="B147">
@@ -1984,8 +1992,8 @@
         <v>1.943888888888889</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2">
+    <row r="148" spans="1:3">
+      <c r="A148" s="1">
         <v>43030</v>
       </c>
       <c r="B148">
@@ -1995,8 +2003,8 @@
         <v>1.831666666666667</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2">
+    <row r="149" spans="1:3">
+      <c r="A149" s="1">
         <v>43037</v>
       </c>
       <c r="B149">
@@ -2006,8 +2014,8 @@
         <v>1.851851851851852</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2">
+    <row r="150" spans="1:3">
+      <c r="A150" s="1">
         <v>43044</v>
       </c>
       <c r="B150">
@@ -2017,8 +2025,8 @@
         <v>1.837222222222222</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2">
+    <row r="151" spans="1:3">
+      <c r="A151" s="1">
         <v>43051</v>
       </c>
       <c r="B151">
@@ -2028,8 +2036,8 @@
         <v>1.797777777777778</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2">
+    <row r="152" spans="1:3">
+      <c r="A152" s="1">
         <v>43058</v>
       </c>
       <c r="B152">
@@ -2039,8 +2047,8 @@
         <v>1.756111111111111</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2">
+    <row r="153" spans="1:3">
+      <c r="A153" s="1">
         <v>43065</v>
       </c>
       <c r="B153">
@@ -2050,8 +2058,8 @@
         <v>1.706111111111111</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2">
+    <row r="154" spans="1:3">
+      <c r="A154" s="1">
         <v>43072</v>
       </c>
       <c r="B154">
@@ -2061,8 +2069,8 @@
         <v>1.62462962962963</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2">
+    <row r="155" spans="1:3">
+      <c r="A155" s="1">
         <v>43079</v>
       </c>
       <c r="B155">
@@ -2072,8 +2080,8 @@
         <v>1.594444444444444</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2">
+    <row r="156" spans="1:3">
+      <c r="A156" s="1">
         <v>43086</v>
       </c>
       <c r="B156">
@@ -2083,8 +2091,8 @@
         <v>1.58962962962963</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2">
+    <row r="157" spans="1:3">
+      <c r="A157" s="1">
         <v>43093</v>
       </c>
       <c r="B157">
@@ -2094,8 +2102,8 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2">
+    <row r="158" spans="1:3">
+      <c r="A158" s="1">
         <v>43100</v>
       </c>
       <c r="B158">
@@ -2105,8 +2113,8 @@
         <v>1.532777777777778</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2">
+    <row r="159" spans="1:3">
+      <c r="A159" s="1">
         <v>43107</v>
       </c>
       <c r="B159">
@@ -2116,8 +2124,8 @@
         <v>1.541111111111111</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2">
+    <row r="160" spans="1:3">
+      <c r="A160" s="1">
         <v>43114</v>
       </c>
       <c r="B160">
@@ -2127,8 +2135,8 @@
         <v>1.584259259259259</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2">
+    <row r="161" spans="1:3">
+      <c r="A161" s="1">
         <v>43121</v>
       </c>
       <c r="B161">
@@ -2138,8 +2146,8 @@
         <v>1.634444444444444</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2">
+    <row r="162" spans="1:3">
+      <c r="A162" s="1">
         <v>43128</v>
       </c>
       <c r="B162">
@@ -2149,8 +2157,8 @@
         <v>1.613148148148148</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2">
+    <row r="163" spans="1:3">
+      <c r="A163" s="1">
         <v>43135</v>
       </c>
       <c r="B163">
@@ -2160,8 +2168,8 @@
         <v>1.542592592592593</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2">
+    <row r="164" spans="1:3">
+      <c r="A164" s="1">
         <v>43142</v>
       </c>
       <c r="B164">
@@ -2171,8 +2179,8 @@
         <v>1.567407407407407</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2">
+    <row r="165" spans="1:3">
+      <c r="A165" s="1">
         <v>43149</v>
       </c>
       <c r="B165">
@@ -2182,8 +2190,8 @@
         <v>1.575925925925926</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2">
+    <row r="166" spans="1:3">
+      <c r="A166" s="1">
         <v>43156</v>
       </c>
       <c r="B166">
@@ -2193,8 +2201,8 @@
         <v>1.578148148148148</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2">
+    <row r="167" spans="1:3">
+      <c r="A167" s="1">
         <v>43163</v>
       </c>
       <c r="B167">
@@ -2204,8 +2212,8 @@
         <v>1.557962962962963</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2">
+    <row r="168" spans="1:3">
+      <c r="A168" s="1">
         <v>43170</v>
       </c>
       <c r="B168">
@@ -2215,8 +2223,8 @@
         <v>1.533518518518519</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2">
+    <row r="169" spans="1:3">
+      <c r="A169" s="1">
         <v>43177</v>
       </c>
       <c r="B169">
@@ -2226,8 +2234,8 @@
         <v>1.531111111111111</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2">
+    <row r="170" spans="1:3">
+      <c r="A170" s="1">
         <v>43184</v>
       </c>
       <c r="B170">
